--- a/AMA/data/Matriks_Waktu_Detik.xlsx
+++ b/AMA/data/Matriks_Waktu_Detik.xlsx
@@ -1,49 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Documents\Semester 8\TA\Coding\Skripsey\AMA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="5835"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,43 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -375,3750 +408,3753 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AI35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1">
+    <row r="1">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C1" t="n">
         <v>1</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" t="n">
         <v>2</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" t="n">
         <v>3</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F1" t="n">
         <v>4</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G1" t="n">
         <v>5</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" t="n">
         <v>6</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I1" t="n">
         <v>7</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J1" t="n">
         <v>8</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" t="n">
         <v>9</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" t="n">
         <v>10</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M1" t="n">
         <v>11</v>
       </c>
-      <c r="N1" s="1">
+      <c r="N1" t="n">
         <v>12</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O1" t="n">
         <v>13</v>
       </c>
-      <c r="P1" s="1">
+      <c r="P1" t="n">
         <v>14</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="Q1" t="n">
         <v>15</v>
       </c>
-      <c r="R1" s="1">
+      <c r="R1" t="n">
         <v>16</v>
       </c>
-      <c r="S1" s="1">
+      <c r="S1" t="n">
         <v>17</v>
       </c>
-      <c r="T1" s="1">
+      <c r="T1" t="n">
         <v>18</v>
       </c>
-      <c r="U1" s="1">
+      <c r="U1" t="n">
         <v>19</v>
       </c>
-      <c r="V1" s="1">
+      <c r="V1" t="n">
         <v>20</v>
       </c>
-      <c r="W1" s="1">
+      <c r="W1" t="n">
         <v>21</v>
       </c>
-      <c r="X1" s="1">
+      <c r="X1" t="n">
         <v>22</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="Y1" t="n">
         <v>23</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Z1" t="n">
         <v>24</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="AA1" t="n">
         <v>25</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="AB1" t="n">
         <v>26</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="AC1" t="n">
         <v>27</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="AD1" t="n">
         <v>28</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="AE1" t="n">
         <v>29</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="AF1" t="n">
         <v>30</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="AG1" t="n">
         <v>31</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="AH1" t="n">
         <v>32</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="AI1" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" t="n">
         <v>193</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" t="n">
         <v>13.1</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" t="n">
         <v>133.6</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" t="n">
         <v>51.3</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" t="n">
         <v>144.4</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" t="n">
         <v>131.9</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" t="n">
         <v>224.4</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" t="n">
         <v>68.3</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" t="n">
         <v>180.7</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" t="n">
         <v>216.6</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" t="n">
         <v>124</v>
       </c>
-      <c r="N2" s="2">
-        <v>87.1</v>
-      </c>
-      <c r="O2" s="2">
+      <c r="N2" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="O2" t="n">
         <v>58.2</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" t="n">
         <v>144.4</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" t="n">
         <v>77.7</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" t="n">
         <v>131.9</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" t="n">
         <v>237.2</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" t="n">
         <v>103.4</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" t="n">
         <v>183.1</v>
       </c>
-      <c r="V2" s="2">
+      <c r="V2" t="n">
         <v>31.5</v>
       </c>
-      <c r="W2" s="2">
+      <c r="W2" t="n">
         <v>102.8</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2" t="n">
         <v>35.1</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y2" t="n">
         <v>55.4</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z2" t="n">
         <v>106.4</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AA2" t="n">
         <v>147.1</v>
       </c>
-      <c r="AB2" s="2">
+      <c r="AB2" t="n">
         <v>115.9</v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AC2" t="n">
         <v>243.2</v>
       </c>
-      <c r="AD2" s="2">
-        <v>73.400000000000006</v>
-      </c>
-      <c r="AE2" s="2">
+      <c r="AD2" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AE2" t="n">
         <v>90.8</v>
       </c>
-      <c r="AF2" s="2">
+      <c r="AF2" t="n">
         <v>157.4</v>
       </c>
-      <c r="AG2" s="2">
-        <v>134.80000000000001</v>
-      </c>
-      <c r="AH2" s="2">
+      <c r="AG2" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="AH2" t="n">
         <v>215.3</v>
       </c>
-      <c r="AI2" s="2">
+      <c r="AI2" t="n">
         <v>90.8</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" t="n">
         <v>146</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" t="n">
         <v>159.1</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" t="n">
         <v>131</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" t="n">
         <v>124.1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" t="n">
         <v>267.8</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" t="n">
         <v>242.6</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" t="n">
         <v>221.8</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" t="n">
         <v>199.8</v>
       </c>
-      <c r="K3" s="2">
-        <v>291.39999999999998</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="L3" t="n">
         <v>327.3</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" t="n">
         <v>136.6</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" t="n">
         <v>127.3</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" t="n">
         <v>204.2</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" t="n">
         <v>267.8</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" t="n">
         <v>201.1</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" t="n">
         <v>242.6</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" t="n">
         <v>111.5</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" t="n">
         <v>214.1</v>
       </c>
-      <c r="U3" s="2">
+      <c r="U3" t="n">
         <v>293.8</v>
       </c>
-      <c r="V3" s="2">
+      <c r="V3" t="n">
         <v>177.5</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" t="n">
         <v>226.2</v>
       </c>
-      <c r="X3" s="2">
+      <c r="X3" t="n">
         <v>181.1</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y3" t="n">
         <v>201.4</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z3" t="n">
         <v>108.8</v>
       </c>
-      <c r="AA3" s="2">
+      <c r="AA3" t="n">
         <v>54.7</v>
       </c>
-      <c r="AB3" s="2">
+      <c r="AB3" t="n">
         <v>239.3</v>
       </c>
-      <c r="AC3" s="2">
+      <c r="AC3" t="n">
         <v>117.5</v>
       </c>
-      <c r="AD3" s="2">
+      <c r="AD3" t="n">
         <v>205.1</v>
       </c>
-      <c r="AE3" s="2">
+      <c r="AE3" t="n">
         <v>148.6</v>
       </c>
-      <c r="AF3" s="2">
-        <v>268.10000000000002</v>
-      </c>
-      <c r="AG3" s="2">
+      <c r="AF3" t="n">
+        <v>268.1</v>
+      </c>
+      <c r="AG3" t="n">
         <v>245.5</v>
       </c>
-      <c r="AH3" s="2">
+      <c r="AH3" t="n">
         <v>126.9</v>
       </c>
-      <c r="AI3" s="2">
+      <c r="AI3" t="n">
         <v>148.6</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" t="n">
         <v>202.5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" t="n">
         <v>148.6</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" t="n">
         <v>66.3</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" t="n">
         <v>143</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" t="n">
         <v>146.9</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" t="n">
         <v>239.4</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" t="n">
         <v>63</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" t="n">
         <v>195.7</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" t="n">
         <v>231.6</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" t="n">
         <v>139</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" t="n">
         <v>102.1</v>
       </c>
-      <c r="O4" s="2">
-        <v>73.099999999999994</v>
-      </c>
-      <c r="P4" s="2">
+      <c r="O4" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="P4" t="n">
         <v>143</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" t="n">
         <v>76.3</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" t="n">
         <v>146.9</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" t="n">
         <v>246.7</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" t="n">
         <v>118.4</v>
       </c>
-      <c r="U4" s="2">
+      <c r="U4" t="n">
         <v>198.1</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" t="n">
         <v>25.8</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" t="n">
         <v>101.4</v>
       </c>
-      <c r="X4" s="2">
+      <c r="X4" t="n">
         <v>55.7</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" t="n">
         <v>49.7</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4" t="n">
         <v>105.9</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AA4" t="n">
         <v>156.6</v>
       </c>
-      <c r="AB4" s="2">
+      <c r="AB4" t="n">
         <v>114.5</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AC4" t="n">
         <v>252.7</v>
       </c>
-      <c r="AD4" s="2">
+      <c r="AD4" t="n">
         <v>67.7</v>
       </c>
-      <c r="AE4" s="2">
+      <c r="AE4" t="n">
         <v>90.3</v>
       </c>
-      <c r="AF4" s="2">
+      <c r="AF4" t="n">
         <v>172.4</v>
       </c>
-      <c r="AG4" s="2">
-        <v>149.80000000000001</v>
-      </c>
-      <c r="AH4" s="2">
+      <c r="AG4" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="AH4" t="n">
         <v>224.8</v>
       </c>
-      <c r="AI4" s="2">
+      <c r="AI4" t="n">
         <v>90.3</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" t="n">
         <v>74.8</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" t="n">
         <v>127.5</v>
       </c>
-      <c r="D5" s="2">
-        <v>87.9</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" t="n">
         <v>52.9</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" t="n">
         <v>196.6</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" t="n">
         <v>171.4</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" t="n">
         <v>90.8</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" t="n">
         <v>128.6</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" t="n">
         <v>220.2</v>
       </c>
-      <c r="L5" s="2">
-        <v>256.10000000000002</v>
-      </c>
-      <c r="M5" s="2">
-        <v>65.400000000000006</v>
-      </c>
-      <c r="N5" s="2">
+      <c r="L5" t="n">
+        <v>256.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="N5" t="n">
         <v>56.1</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" t="n">
         <v>133</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" t="n">
         <v>196.6</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" t="n">
         <v>129.9</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" t="n">
         <v>171.4</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" t="n">
         <v>171.7</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5" t="n">
         <v>142.9</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" t="n">
         <v>222.6</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5" t="n">
         <v>106.3</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5" t="n">
         <v>155</v>
       </c>
-      <c r="X5" s="2">
+      <c r="X5" t="n">
         <v>109.9</v>
       </c>
-      <c r="Y5" s="2">
-        <v>130.19999999999999</v>
-      </c>
-      <c r="Z5" s="2">
+      <c r="Y5" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="Z5" t="n">
         <v>55.5</v>
       </c>
-      <c r="AA5" s="2">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="AB5" s="2">
+      <c r="AA5" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AB5" t="n">
         <v>168.1</v>
       </c>
-      <c r="AC5" s="2">
+      <c r="AC5" t="n">
         <v>177.7</v>
       </c>
-      <c r="AD5" s="2">
-        <v>148.19999999999999</v>
-      </c>
-      <c r="AE5" s="2">
+      <c r="AD5" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="AE5" t="n">
         <v>95.3</v>
       </c>
-      <c r="AF5" s="2">
+      <c r="AF5" t="n">
         <v>196.9</v>
       </c>
-      <c r="AG5" s="2">
+      <c r="AG5" t="n">
         <v>174.3</v>
       </c>
-      <c r="AH5" s="2">
-        <v>149.80000000000001</v>
-      </c>
-      <c r="AI5" s="2">
+      <c r="AH5" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="AI5" t="n">
         <v>95.3</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" t="n">
         <v>21.9</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" t="n">
         <v>179.6</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" t="n">
         <v>35</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" t="n">
         <v>120.2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2">
-        <v>143.69999999999999</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="G6" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="H6" t="n">
         <v>118.5</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" t="n">
         <v>211</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" t="n">
         <v>75.7</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" t="n">
         <v>167.3</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" t="n">
         <v>203.2</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" t="n">
         <v>110.6</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" t="n">
         <v>73.7</v>
       </c>
-      <c r="O6" s="2">
-        <v>80.099999999999994</v>
-      </c>
-      <c r="P6" s="2">
-        <v>143.69999999999999</v>
-      </c>
-      <c r="Q6" s="2">
+      <c r="O6" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="P6" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="Q6" t="n">
         <v>77</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" t="n">
         <v>118.5</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" t="n">
         <v>223.8</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6" t="n">
         <v>90</v>
       </c>
-      <c r="U6" s="2">
+      <c r="U6" t="n">
         <v>169.7</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6" t="n">
         <v>53.4</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6" t="n">
         <v>102.1</v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6" t="n">
         <v>57</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6" t="n">
         <v>77.3</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" t="n">
         <v>107.6</v>
       </c>
-      <c r="AA6" s="2">
-        <v>133.69999999999999</v>
-      </c>
-      <c r="AB6" s="2">
+      <c r="AA6" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="AB6" t="n">
         <v>115.2</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AC6" t="n">
         <v>229.8</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AD6" t="n">
         <v>95.3</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AE6" t="n">
         <v>112.7</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AF6" t="n">
         <v>144</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AG6" t="n">
         <v>121.4</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AH6" t="n">
         <v>201.9</v>
       </c>
-      <c r="AI6" s="2">
+      <c r="AI6" t="n">
         <v>112.7</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <v>141.80000000000001</v>
-      </c>
-      <c r="C7" s="2">
-        <v>299.39999999999998</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="D7" t="n">
         <v>152.4</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" t="n">
         <v>249.5</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" t="n">
         <v>193.1</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" t="n">
         <v>212.8</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" t="n">
         <v>340.3</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" t="n">
         <v>101.4</v>
       </c>
-      <c r="K7" s="2">
-        <v>261.60000000000002</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="K7" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="L7" t="n">
         <v>220.7</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" t="n">
         <v>239.9</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" t="n">
         <v>203</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" t="n">
         <v>111.5</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="2">
-        <v>80.599999999999994</v>
-      </c>
-      <c r="R7" s="2">
+      <c r="Q7" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="R7" t="n">
         <v>212.8</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" t="n">
         <v>343.6</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T7" t="n">
         <v>184.3</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" t="n">
         <v>264</v>
       </c>
-      <c r="V7" s="2">
-        <v>146.80000000000001</v>
-      </c>
-      <c r="W7" s="2">
+      <c r="V7" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="W7" t="n">
         <v>41.3</v>
       </c>
-      <c r="X7" s="2">
+      <c r="X7" t="n">
         <v>105.6</v>
       </c>
-      <c r="Y7" s="2">
-        <v>90.6</v>
-      </c>
-      <c r="Z7" s="2">
+      <c r="Y7" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z7" t="n">
         <v>202.8</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AA7" t="n">
         <v>253.5</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AB7" t="n">
         <v>43.4</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AC7" t="n">
         <v>349.6</v>
       </c>
-      <c r="AD7" s="2">
-        <v>151.30000000000001</v>
-      </c>
-      <c r="AE7" s="2">
+      <c r="AD7" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="AE7" t="n">
         <v>187.2</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AF7" t="n">
         <v>230.4</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AG7" t="n">
         <v>250.7</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AH7" t="n">
         <v>321.7</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AI7" t="n">
         <v>187.2</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" t="n">
         <v>248.9</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" t="n">
         <v>318.5</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" t="n">
         <v>262</v>
       </c>
-      <c r="E8" s="2">
-        <v>259.10000000000002</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="E8" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="F8" t="n">
         <v>227</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" t="n">
         <v>320</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" t="n">
         <v>349.9</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" t="n">
         <v>258.2</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" t="n">
         <v>48.8</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" t="n">
         <v>192.4</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" t="n">
         <v>249.5</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" t="n">
         <v>212.6</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" t="n">
         <v>268.7</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" t="n">
         <v>320</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" t="n">
         <v>259.5</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" t="n">
         <v>362.7</v>
       </c>
-      <c r="T8" s="2">
+      <c r="T8" t="n">
         <v>209.1</v>
       </c>
-      <c r="U8" s="2">
+      <c r="U8" t="n">
         <v>51.2</v>
       </c>
-      <c r="V8" s="2">
-        <v>280.39999999999998</v>
-      </c>
-      <c r="W8" s="2">
-        <v>284.60000000000002</v>
-      </c>
-      <c r="X8" s="2">
+      <c r="V8" t="n">
+        <v>280.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="X8" t="n">
         <v>251.8</v>
       </c>
-      <c r="Y8" s="2">
-        <v>262.89999999999998</v>
-      </c>
-      <c r="Z8" s="2">
+      <c r="Y8" t="n">
+        <v>262.9</v>
+      </c>
+      <c r="Z8" t="n">
         <v>246.5</v>
       </c>
-      <c r="AA8" s="2">
-        <v>272.60000000000002</v>
-      </c>
-      <c r="AB8" s="2">
+      <c r="AA8" t="n">
+        <v>272.6</v>
+      </c>
+      <c r="AB8" t="n">
         <v>297.7</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AC8" t="n">
         <v>368.7</v>
       </c>
-      <c r="AD8" s="2">
+      <c r="AD8" t="n">
         <v>322.3</v>
       </c>
-      <c r="AE8" s="2">
+      <c r="AE8" t="n">
         <v>286.3</v>
       </c>
-      <c r="AF8" s="2">
+      <c r="AF8" t="n">
         <v>176.8</v>
       </c>
-      <c r="AG8" s="2">
+      <c r="AG8" t="n">
         <v>260.3</v>
       </c>
-      <c r="AH8" s="2">
+      <c r="AH8" t="n">
         <v>340.8</v>
       </c>
-      <c r="AI8" s="2">
+      <c r="AI8" t="n">
         <v>286.3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" t="n">
         <v>165.6</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" t="n">
         <v>218.3</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" t="n">
         <v>178.7</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" t="n">
         <v>90.8</v>
       </c>
-      <c r="F9" s="2">
-        <v>143.69999999999999</v>
-      </c>
-      <c r="G9" s="2">
-        <v>287.39999999999998</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="F9" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="H9" t="n">
         <v>262.2</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" t="n">
         <v>219.4</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" t="n">
         <v>311</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" t="n">
         <v>346.9</v>
       </c>
-      <c r="M9" s="2">
-        <v>156.19999999999999</v>
-      </c>
-      <c r="N9" s="2">
+      <c r="M9" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="N9" t="n">
         <v>146.9</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" t="n">
         <v>223.8</v>
       </c>
-      <c r="P9" s="2">
-        <v>287.39999999999998</v>
-      </c>
-      <c r="Q9" s="2">
+      <c r="P9" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="Q9" t="n">
         <v>220.7</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" t="n">
         <v>262.2</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S9" t="n">
         <v>248.1</v>
       </c>
-      <c r="T9" s="2">
+      <c r="T9" t="n">
         <v>233.7</v>
       </c>
-      <c r="U9" s="2">
-        <v>313.39999999999998</v>
-      </c>
-      <c r="V9" s="2">
+      <c r="U9" t="n">
+        <v>313.4</v>
+      </c>
+      <c r="V9" t="n">
         <v>197.1</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" t="n">
         <v>245.8</v>
       </c>
-      <c r="X9" s="2">
+      <c r="X9" t="n">
         <v>200.7</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y9" t="n">
         <v>221</v>
       </c>
-      <c r="Z9" s="2">
-        <v>146.30000000000001</v>
-      </c>
-      <c r="AA9" s="2">
+      <c r="Z9" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="AA9" t="n">
         <v>172.4</v>
       </c>
-      <c r="AB9" s="2">
-        <v>258.89999999999998</v>
-      </c>
-      <c r="AC9" s="2">
+      <c r="AB9" t="n">
+        <v>258.9</v>
+      </c>
+      <c r="AC9" t="n">
         <v>258.7</v>
       </c>
-      <c r="AD9" s="2">
+      <c r="AD9" t="n">
         <v>239</v>
       </c>
-      <c r="AE9" s="2">
+      <c r="AE9" t="n">
         <v>186.1</v>
       </c>
-      <c r="AF9" s="2">
+      <c r="AF9" t="n">
         <v>287.7</v>
       </c>
-      <c r="AG9" s="2">
-        <v>265.10000000000002</v>
-      </c>
-      <c r="AH9" s="2">
+      <c r="AG9" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="AH9" t="n">
         <v>169.8</v>
       </c>
-      <c r="AI9" s="2">
+      <c r="AI9" t="n">
         <v>186.1</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" t="n">
         <v>66.8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" t="n">
         <v>227.3</v>
       </c>
-      <c r="D10" s="2">
-        <v>77.400000000000006</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D10" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="E10" t="n">
         <v>183</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" t="n">
         <v>118.1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" t="n">
         <v>100.4</v>
       </c>
-      <c r="H10" s="2">
-        <v>146.30000000000001</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="H10" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="I10" t="n">
         <v>273.8</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" t="n">
         <v>195.1</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" t="n">
         <v>231</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" t="n">
         <v>173.4</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" t="n">
         <v>136.5</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" t="n">
         <v>10.1</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" t="n">
         <v>100.4</v>
       </c>
-      <c r="Q10" s="2">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="R10" s="2">
-        <v>146.30000000000001</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="Q10" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="S10" t="n">
         <v>271.5</v>
       </c>
-      <c r="T10" s="2">
+      <c r="T10" t="n">
         <v>117.8</v>
       </c>
-      <c r="U10" s="2">
+      <c r="U10" t="n">
         <v>197.5</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10" t="n">
         <v>74.7</v>
       </c>
-      <c r="W10" s="2">
+      <c r="W10" t="n">
         <v>58.8</v>
       </c>
-      <c r="X10" s="2">
+      <c r="X10" t="n">
         <v>30.6</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y10" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z10" s="2">
-        <v>130.69999999999999</v>
-      </c>
-      <c r="AA10" s="2">
+      <c r="Z10" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="AA10" t="n">
         <v>181.4</v>
       </c>
-      <c r="AB10" s="2">
-        <v>71.900000000000006</v>
-      </c>
-      <c r="AC10" s="2">
+      <c r="AB10" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AC10" t="n">
         <v>277.5</v>
       </c>
-      <c r="AD10" s="2">
+      <c r="AD10" t="n">
         <v>79.2</v>
       </c>
-      <c r="AE10" s="2">
+      <c r="AE10" t="n">
         <v>115.1</v>
       </c>
-      <c r="AF10" s="2">
+      <c r="AF10" t="n">
         <v>171.8</v>
       </c>
-      <c r="AG10" s="2">
+      <c r="AG10" t="n">
         <v>184.2</v>
       </c>
-      <c r="AH10" s="2">
+      <c r="AH10" t="n">
         <v>249.6</v>
       </c>
-      <c r="AI10" s="2">
+      <c r="AI10" t="n">
         <v>115.1</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
-        <v>256.10000000000002</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" t="n">
+        <v>256.1</v>
+      </c>
+      <c r="C11" t="n">
         <v>325.7</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" t="n">
         <v>269.2</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" t="n">
         <v>266.3</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" t="n">
         <v>234.2</v>
       </c>
-      <c r="G11" s="2">
-        <v>295.60000000000002</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="G11" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="H11" t="n">
         <v>158.5</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" t="n">
         <v>357.1</v>
       </c>
-      <c r="J11" s="2">
-        <v>265.39999999999998</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="J11" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" t="n">
         <v>168</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" t="n">
         <v>256.7</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" t="n">
         <v>219.8</v>
       </c>
-      <c r="O11" s="2">
-        <v>275.89999999999998</v>
-      </c>
-      <c r="P11" s="2">
-        <v>295.60000000000002</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="O11" t="n">
+        <v>275.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="Q11" t="n">
         <v>266.7</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" t="n">
         <v>158.5</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" t="n">
         <v>369.9</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" t="n">
         <v>216.3</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" t="n">
         <v>23.9</v>
       </c>
-      <c r="V11" s="2">
-        <v>287.60000000000002</v>
-      </c>
-      <c r="W11" s="2">
+      <c r="V11" t="n">
+        <v>287.6</v>
+      </c>
+      <c r="W11" t="n">
         <v>291.8</v>
       </c>
-      <c r="X11" s="2">
+      <c r="X11" t="n">
         <v>259</v>
       </c>
-      <c r="Y11" s="2">
-        <v>270.10000000000002</v>
-      </c>
-      <c r="Z11" s="2">
+      <c r="Y11" t="n">
+        <v>270.1</v>
+      </c>
+      <c r="Z11" t="n">
         <v>253.7</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AA11" t="n">
         <v>279.8</v>
       </c>
-      <c r="AB11" s="2">
-        <v>304.89999999999998</v>
-      </c>
-      <c r="AC11" s="2">
+      <c r="AB11" t="n">
+        <v>304.9</v>
+      </c>
+      <c r="AC11" t="n">
         <v>375.9</v>
       </c>
-      <c r="AD11" s="2">
+      <c r="AD11" t="n">
         <v>329.5</v>
       </c>
-      <c r="AE11" s="2">
+      <c r="AE11" t="n">
         <v>293.5</v>
       </c>
-      <c r="AF11" s="2">
+      <c r="AF11" t="n">
         <v>177.7</v>
       </c>
-      <c r="AG11" s="2">
+      <c r="AG11" t="n">
         <v>267.5</v>
       </c>
-      <c r="AH11" s="2">
+      <c r="AH11" t="n">
         <v>348</v>
       </c>
-      <c r="AI11" s="2">
+      <c r="AI11" t="n">
         <v>293.5</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" t="n">
         <v>298.3</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" t="n">
         <v>367.9</v>
       </c>
-      <c r="D12" s="2">
-        <v>311.39999999999998</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="D12" t="n">
+        <v>311.4</v>
+      </c>
+      <c r="E12" t="n">
         <v>308.5</v>
       </c>
-      <c r="F12" s="2">
-        <v>276.39999999999998</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="F12" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="G12" t="n">
         <v>235.3</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" t="n">
         <v>130</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" t="n">
         <v>399.3</v>
       </c>
-      <c r="J12" s="2">
-        <v>307.60000000000002</v>
-      </c>
-      <c r="K12" s="2">
+      <c r="J12" t="n">
+        <v>307.6</v>
+      </c>
+      <c r="K12" t="n">
         <v>178.8</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="2">
-        <v>298.89999999999998</v>
-      </c>
-      <c r="N12" s="2">
+      <c r="M12" t="n">
+        <v>298.9</v>
+      </c>
+      <c r="N12" t="n">
         <v>262</v>
       </c>
-      <c r="O12" s="2">
-        <v>318.10000000000002</v>
-      </c>
-      <c r="P12" s="2">
+      <c r="O12" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="P12" t="n">
         <v>235.3</v>
       </c>
-      <c r="Q12" s="2">
-        <v>308.89999999999998</v>
-      </c>
-      <c r="R12" s="2">
+      <c r="Q12" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="R12" t="n">
         <v>130</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" t="n">
         <v>412.1</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T12" t="n">
         <v>258.5</v>
       </c>
-      <c r="U12" s="2">
+      <c r="U12" t="n">
         <v>181.2</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V12" t="n">
         <v>329.8</v>
       </c>
-      <c r="W12" s="2">
-        <v>276.60000000000002</v>
-      </c>
-      <c r="X12" s="2">
+      <c r="W12" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="X12" t="n">
         <v>301.2</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y12" t="n">
         <v>312.3</v>
       </c>
-      <c r="Z12" s="2">
-        <v>295.89999999999998</v>
-      </c>
-      <c r="AA12" s="2">
+      <c r="Z12" t="n">
+        <v>295.9</v>
+      </c>
+      <c r="AA12" t="n">
         <v>322</v>
       </c>
-      <c r="AB12" s="2">
+      <c r="AB12" t="n">
         <v>278.7</v>
       </c>
-      <c r="AC12" s="2">
+      <c r="AC12" t="n">
         <v>418.1</v>
       </c>
-      <c r="AD12" s="2">
+      <c r="AD12" t="n">
         <v>371.7</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AE12" t="n">
         <v>335.7</v>
       </c>
-      <c r="AF12" s="2">
+      <c r="AF12" t="n">
         <v>55.7</v>
       </c>
-      <c r="AG12" s="2">
+      <c r="AG12" t="n">
         <v>309.7</v>
       </c>
-      <c r="AH12" s="2">
+      <c r="AH12" t="n">
         <v>390.2</v>
       </c>
-      <c r="AI12" s="2">
+      <c r="AI12" t="n">
         <v>335.7</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" t="n">
         <v>55</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" t="n">
         <v>133</v>
       </c>
-      <c r="D13" s="2">
-        <v>68.099999999999994</v>
-      </c>
-      <c r="E13" s="2">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="D13" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="F13" t="n">
         <v>33.1</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" t="n">
         <v>176.8</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" t="n">
         <v>151.6</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" t="n">
         <v>164.4</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" t="n">
         <v>108.8</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" t="n">
         <v>200.4</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" t="n">
         <v>236.3</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="2">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="O13" s="2">
+      <c r="N13" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="O13" t="n">
         <v>113.2</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" t="n">
         <v>176.8</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" t="n">
         <v>110.1</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" t="n">
         <v>151.6</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" t="n">
         <v>177.2</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T13" t="n">
         <v>123.1</v>
       </c>
-      <c r="U13" s="2">
+      <c r="U13" t="n">
         <v>202.8</v>
       </c>
-      <c r="V13" s="2">
+      <c r="V13" t="n">
         <v>86.5</v>
       </c>
-      <c r="W13" s="2">
-        <v>135.19999999999999</v>
-      </c>
-      <c r="X13" s="2">
-        <v>90.1</v>
-      </c>
-      <c r="Y13" s="2">
+      <c r="W13" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="Y13" t="n">
         <v>110.4</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="Z13" t="n">
         <v>61</v>
       </c>
-      <c r="AA13" s="2">
-        <v>87.1</v>
-      </c>
-      <c r="AB13" s="2">
-        <v>148.30000000000001</v>
-      </c>
-      <c r="AC13" s="2">
+      <c r="AA13" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="AC13" t="n">
         <v>183.2</v>
       </c>
-      <c r="AD13" s="2">
+      <c r="AD13" t="n">
         <v>128.4</v>
       </c>
-      <c r="AE13" s="2">
+      <c r="AE13" t="n">
         <v>100.8</v>
       </c>
-      <c r="AF13" s="2">
+      <c r="AF13" t="n">
         <v>177.1</v>
       </c>
-      <c r="AG13" s="2">
+      <c r="AG13" t="n">
         <v>154.5</v>
       </c>
-      <c r="AH13" s="2">
-        <v>155.30000000000001</v>
-      </c>
-      <c r="AI13" s="2">
+      <c r="AH13" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="AI13" t="n">
         <v>100.8</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" t="n">
         <v>46.3</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" t="n">
         <v>105.9</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" t="n">
         <v>59.4</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" t="n">
         <v>46.5</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" t="n">
         <v>24.4</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" t="n">
         <v>168.1</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" t="n">
         <v>142.9</v>
       </c>
-      <c r="I14" s="2">
-        <v>137.30000000000001</v>
-      </c>
-      <c r="J14" s="2">
+      <c r="I14" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="J14" t="n">
         <v>100.1</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" t="n">
         <v>191.7</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" t="n">
         <v>227.6</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" t="n">
         <v>36.9</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14" t="n">
         <v>104.5</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" t="n">
         <v>168.1</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" t="n">
         <v>101.4</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" t="n">
         <v>142.9</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" t="n">
         <v>150.1</v>
       </c>
-      <c r="T14" s="2">
+      <c r="T14" t="n">
         <v>114.4</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" t="n">
         <v>194.1</v>
       </c>
-      <c r="V14" s="2">
+      <c r="V14" t="n">
         <v>77.8</v>
       </c>
-      <c r="W14" s="2">
+      <c r="W14" t="n">
         <v>126.5</v>
       </c>
-      <c r="X14" s="2">
-        <v>81.400000000000006</v>
-      </c>
-      <c r="Y14" s="2">
+      <c r="X14" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="Y14" t="n">
         <v>101.7</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="Z14" t="n">
         <v>33.9</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AA14" t="n">
         <v>60</v>
       </c>
-      <c r="AB14" s="2">
+      <c r="AB14" t="n">
         <v>139.6</v>
       </c>
-      <c r="AC14" s="2">
+      <c r="AC14" t="n">
         <v>156.1</v>
       </c>
-      <c r="AD14" s="2">
+      <c r="AD14" t="n">
         <v>119.7</v>
       </c>
-      <c r="AE14" s="2">
+      <c r="AE14" t="n">
         <v>73.7</v>
       </c>
-      <c r="AF14" s="2">
+      <c r="AF14" t="n">
         <v>168.4</v>
       </c>
-      <c r="AG14" s="2">
-        <v>145.80000000000001</v>
-      </c>
-      <c r="AH14" s="2">
-        <v>128.19999999999999</v>
-      </c>
-      <c r="AI14" s="2">
+      <c r="AG14" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="AI14" t="n">
         <v>73.7</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" t="n">
         <v>56.7</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" t="n">
         <v>237.4</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" t="n">
         <v>67.3</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" t="n">
         <v>185.6</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" t="n">
         <v>108</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" t="n">
         <v>110.5</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" t="n">
         <v>148.9</v>
       </c>
-      <c r="I15" s="2">
-        <v>276.39999999999998</v>
-      </c>
-      <c r="J15" s="2">
+      <c r="I15" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="J15" t="n">
         <v>10.1</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" t="n">
         <v>197.7</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" t="n">
         <v>233.6</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" t="n">
         <v>176</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" t="n">
         <v>139.1</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" t="n">
         <v>110.5</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" t="n">
         <v>43.8</v>
       </c>
-      <c r="R15" s="2">
+      <c r="R15" t="n">
         <v>148.9</v>
       </c>
-      <c r="S15" s="2">
-        <v>281.60000000000002</v>
-      </c>
-      <c r="T15" s="2">
+      <c r="S15" t="n">
+        <v>281.6</v>
+      </c>
+      <c r="T15" t="n">
         <v>120.4</v>
       </c>
-      <c r="U15" s="2">
+      <c r="U15" t="n">
         <v>200.1</v>
       </c>
-      <c r="V15" s="2">
+      <c r="V15" t="n">
         <v>84.8</v>
       </c>
-      <c r="W15" s="2">
-        <v>68.900000000000006</v>
-      </c>
-      <c r="X15" s="2">
+      <c r="W15" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="X15" t="n">
         <v>20.5</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" t="n">
         <v>28.6</v>
       </c>
-      <c r="Z15" s="2">
-        <v>140.80000000000001</v>
-      </c>
-      <c r="AA15" s="2">
+      <c r="Z15" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="AA15" t="n">
         <v>191.5</v>
       </c>
-      <c r="AB15" s="2">
+      <c r="AB15" t="n">
         <v>82</v>
       </c>
-      <c r="AC15" s="2">
-        <v>287.60000000000002</v>
-      </c>
-      <c r="AD15" s="2">
+      <c r="AC15" t="n">
+        <v>287.6</v>
+      </c>
+      <c r="AD15" t="n">
         <v>89.3</v>
       </c>
-      <c r="AE15" s="2">
+      <c r="AE15" t="n">
         <v>125.2</v>
       </c>
-      <c r="AF15" s="2">
+      <c r="AF15" t="n">
         <v>174.4</v>
       </c>
-      <c r="AG15" s="2">
+      <c r="AG15" t="n">
         <v>186.8</v>
       </c>
-      <c r="AH15" s="2">
+      <c r="AH15" t="n">
         <v>259.7</v>
       </c>
-      <c r="AI15" s="2">
+      <c r="AI15" t="n">
         <v>125.2</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
-        <v>141.80000000000001</v>
-      </c>
-      <c r="C16" s="2">
-        <v>299.39999999999998</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="B16" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="D16" t="n">
         <v>152.4</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" t="n">
         <v>249.5</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" t="n">
         <v>193.1</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" t="n">
         <v>212.8</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" t="n">
         <v>340.3</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" t="n">
         <v>101.4</v>
       </c>
-      <c r="K16" s="2">
-        <v>261.60000000000002</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="K16" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="L16" t="n">
         <v>220.7</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" t="n">
         <v>239.9</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" t="n">
         <v>203</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16" t="n">
         <v>111.5</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="2">
-        <v>80.599999999999994</v>
-      </c>
-      <c r="R16" s="2">
+      <c r="Q16" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="R16" t="n">
         <v>212.8</v>
       </c>
-      <c r="S16" s="2">
+      <c r="S16" t="n">
         <v>343.6</v>
       </c>
-      <c r="T16" s="2">
+      <c r="T16" t="n">
         <v>184.3</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" t="n">
         <v>264</v>
       </c>
-      <c r="V16" s="2">
-        <v>146.80000000000001</v>
-      </c>
-      <c r="W16" s="2">
+      <c r="V16" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="W16" t="n">
         <v>41.3</v>
       </c>
-      <c r="X16" s="2">
+      <c r="X16" t="n">
         <v>105.6</v>
       </c>
-      <c r="Y16" s="2">
-        <v>90.6</v>
-      </c>
-      <c r="Z16" s="2">
+      <c r="Y16" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z16" t="n">
         <v>202.8</v>
       </c>
-      <c r="AA16" s="2">
+      <c r="AA16" t="n">
         <v>253.5</v>
       </c>
-      <c r="AB16" s="2">
+      <c r="AB16" t="n">
         <v>43.4</v>
       </c>
-      <c r="AC16" s="2">
+      <c r="AC16" t="n">
         <v>349.6</v>
       </c>
-      <c r="AD16" s="2">
-        <v>151.30000000000001</v>
-      </c>
-      <c r="AE16" s="2">
+      <c r="AD16" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="AE16" t="n">
         <v>187.2</v>
       </c>
-      <c r="AF16" s="2">
+      <c r="AF16" t="n">
         <v>230.4</v>
       </c>
-      <c r="AG16" s="2">
+      <c r="AG16" t="n">
         <v>250.7</v>
       </c>
-      <c r="AH16" s="2">
+      <c r="AH16" t="n">
         <v>321.7</v>
       </c>
-      <c r="AI16" s="2">
+      <c r="AI16" t="n">
         <v>187.2</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" t="n">
         <v>77.2</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" t="n">
         <v>234.8</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" t="n">
         <v>87.8</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" t="n">
         <v>184.9</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" t="n">
         <v>128.5</v>
       </c>
-      <c r="G17" s="2">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="H17" s="2">
-        <v>148.19999999999999</v>
-      </c>
-      <c r="I17" s="2">
+      <c r="G17" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="I17" t="n">
         <v>275.7</v>
       </c>
-      <c r="J17" s="2">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="K17" s="2">
+      <c r="J17" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="K17" t="n">
         <v>197</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" t="n">
         <v>232.9</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" t="n">
         <v>175.3</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" t="n">
         <v>138.4</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17" t="n">
         <v>46.9</v>
       </c>
-      <c r="P17" s="2">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="Q17" s="2">
+      <c r="P17" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="R17" s="2">
-        <v>148.19999999999999</v>
-      </c>
-      <c r="S17" s="2">
+      <c r="R17" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="S17" t="n">
         <v>279</v>
       </c>
-      <c r="T17" s="2">
+      <c r="T17" t="n">
         <v>119.7</v>
       </c>
-      <c r="U17" s="2">
+      <c r="U17" t="n">
         <v>199.4</v>
       </c>
-      <c r="V17" s="2">
+      <c r="V17" t="n">
         <v>82.2</v>
       </c>
-      <c r="W17" s="2">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="X17" s="2">
+      <c r="W17" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="X17" t="n">
         <v>41</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y17" t="n">
         <v>26</v>
       </c>
-      <c r="Z17" s="2">
-        <v>138.19999999999999</v>
-      </c>
-      <c r="AA17" s="2">
+      <c r="Z17" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="AA17" t="n">
         <v>188.9</v>
       </c>
-      <c r="AB17" s="2">
+      <c r="AB17" t="n">
         <v>47.4</v>
       </c>
-      <c r="AC17" s="2">
+      <c r="AC17" t="n">
         <v>285</v>
       </c>
-      <c r="AD17" s="2">
+      <c r="AD17" t="n">
         <v>86.7</v>
       </c>
-      <c r="AE17" s="2">
+      <c r="AE17" t="n">
         <v>122.6</v>
       </c>
-      <c r="AF17" s="2">
+      <c r="AF17" t="n">
         <v>173.7</v>
       </c>
-      <c r="AG17" s="2">
+      <c r="AG17" t="n">
         <v>186.1</v>
       </c>
-      <c r="AH17" s="2">
-        <v>257.10000000000002</v>
-      </c>
-      <c r="AI17" s="2">
+      <c r="AH17" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="AI17" t="n">
         <v>122.6</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" t="n">
         <v>248.9</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" t="n">
         <v>318.5</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" t="n">
         <v>262</v>
       </c>
-      <c r="E18" s="2">
-        <v>259.10000000000002</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="E18" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="F18" t="n">
         <v>227</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" t="n">
         <v>320</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" t="n">
         <v>349.9</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" t="n">
         <v>258.2</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" t="n">
         <v>48.8</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" t="n">
         <v>192.4</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" t="n">
         <v>249.5</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" t="n">
         <v>212.6</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18" t="n">
         <v>268.7</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" t="n">
         <v>320</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" t="n">
         <v>259.5</v>
       </c>
-      <c r="R18" s="2">
+      <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="2">
+      <c r="S18" t="n">
         <v>362.7</v>
       </c>
-      <c r="T18" s="2">
+      <c r="T18" t="n">
         <v>209.1</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" t="n">
         <v>51.2</v>
       </c>
-      <c r="V18" s="2">
-        <v>280.39999999999998</v>
-      </c>
-      <c r="W18" s="2">
-        <v>284.60000000000002</v>
-      </c>
-      <c r="X18" s="2">
+      <c r="V18" t="n">
+        <v>280.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="X18" t="n">
         <v>251.8</v>
       </c>
-      <c r="Y18" s="2">
-        <v>262.89999999999998</v>
-      </c>
-      <c r="Z18" s="2">
+      <c r="Y18" t="n">
+        <v>262.9</v>
+      </c>
+      <c r="Z18" t="n">
         <v>246.5</v>
       </c>
-      <c r="AA18" s="2">
-        <v>272.60000000000002</v>
-      </c>
-      <c r="AB18" s="2">
+      <c r="AA18" t="n">
+        <v>272.6</v>
+      </c>
+      <c r="AB18" t="n">
         <v>297.7</v>
       </c>
-      <c r="AC18" s="2">
+      <c r="AC18" t="n">
         <v>368.7</v>
       </c>
-      <c r="AD18" s="2">
+      <c r="AD18" t="n">
         <v>322.3</v>
       </c>
-      <c r="AE18" s="2">
+      <c r="AE18" t="n">
         <v>286.3</v>
       </c>
-      <c r="AF18" s="2">
+      <c r="AF18" t="n">
         <v>176.8</v>
       </c>
-      <c r="AG18" s="2">
+      <c r="AG18" t="n">
         <v>260.3</v>
       </c>
-      <c r="AH18" s="2">
+      <c r="AH18" t="n">
         <v>340.8</v>
       </c>
-      <c r="AI18" s="2">
+      <c r="AI18" t="n">
         <v>286.3</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" t="n">
         <v>179</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" t="n">
         <v>108.7</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" t="n">
         <v>192.1</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" t="n">
         <v>164</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" t="n">
         <v>157.1</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" t="n">
         <v>300.8</v>
       </c>
-      <c r="H19" s="2">
-        <v>275.60000000000002</v>
-      </c>
-      <c r="I19" s="2">
+      <c r="H19" t="n">
+        <v>275.6</v>
+      </c>
+      <c r="I19" t="n">
         <v>245.4</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" t="n">
         <v>232.8</v>
       </c>
-      <c r="K19" s="2">
-        <v>324.39999999999998</v>
-      </c>
-      <c r="L19" s="2">
+      <c r="K19" t="n">
+        <v>324.4</v>
+      </c>
+      <c r="L19" t="n">
         <v>360.3</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19" t="n">
         <v>169.6</v>
       </c>
-      <c r="N19" s="2">
-        <v>160.30000000000001</v>
-      </c>
-      <c r="O19" s="2">
+      <c r="N19" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="O19" t="n">
         <v>237.2</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" t="n">
         <v>300.8</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" t="n">
         <v>234.1</v>
       </c>
-      <c r="R19" s="2">
-        <v>275.60000000000002</v>
-      </c>
-      <c r="S19" s="2">
+      <c r="R19" t="n">
+        <v>275.6</v>
+      </c>
+      <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="2">
+      <c r="T19" t="n">
         <v>247.1</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" t="n">
         <v>326.8</v>
       </c>
-      <c r="V19" s="2">
+      <c r="V19" t="n">
         <v>210.5</v>
       </c>
-      <c r="W19" s="2">
+      <c r="W19" t="n">
         <v>259.2</v>
       </c>
-      <c r="X19" s="2">
+      <c r="X19" t="n">
         <v>214.1</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y19" t="n">
         <v>234.4</v>
       </c>
-      <c r="Z19" s="2">
-        <v>141.80000000000001</v>
-      </c>
-      <c r="AA19" s="2">
+      <c r="Z19" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="AA19" t="n">
         <v>87.7</v>
       </c>
-      <c r="AB19" s="2">
+      <c r="AB19" t="n">
         <v>272.3</v>
       </c>
-      <c r="AC19" s="2">
+      <c r="AC19" t="n">
         <v>50.5</v>
       </c>
-      <c r="AD19" s="2">
+      <c r="AD19" t="n">
         <v>238.1</v>
       </c>
-      <c r="AE19" s="2">
+      <c r="AE19" t="n">
         <v>181.6</v>
       </c>
-      <c r="AF19" s="2">
-        <v>301.10000000000002</v>
-      </c>
-      <c r="AG19" s="2">
+      <c r="AF19" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="AG19" t="n">
         <v>278.5</v>
       </c>
-      <c r="AH19" s="2">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="AI19" s="2">
+      <c r="AH19" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AI19" t="n">
         <v>181.6</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" t="n">
         <v>218.9</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" t="n">
         <v>288.5</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" t="n">
         <v>232</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" t="n">
         <v>229.1</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" t="n">
         <v>197</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" t="n">
         <v>237.2</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" t="n">
         <v>84.2</v>
       </c>
-      <c r="I20" s="2">
-        <v>319.89999999999998</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="I20" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="J20" t="n">
         <v>228.2</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20" t="n">
         <v>133</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" t="n">
         <v>168.9</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20" t="n">
         <v>219.5</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" t="n">
         <v>182.6</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20" t="n">
         <v>238.7</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" t="n">
         <v>237.2</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" t="n">
         <v>229.5</v>
       </c>
-      <c r="R20" s="2">
+      <c r="R20" t="n">
         <v>84.2</v>
       </c>
-      <c r="S20" s="2">
+      <c r="S20" t="n">
         <v>332.7</v>
       </c>
-      <c r="T20" s="2">
+      <c r="T20" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" t="n">
         <v>135.4</v>
       </c>
-      <c r="V20" s="2">
+      <c r="V20" t="n">
         <v>250.4</v>
       </c>
-      <c r="W20" s="2">
+      <c r="W20" t="n">
         <v>254.6</v>
       </c>
-      <c r="X20" s="2">
+      <c r="X20" t="n">
         <v>221.8</v>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y20" t="n">
         <v>232.9</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="Z20" t="n">
         <v>216.5</v>
       </c>
-      <c r="AA20" s="2">
+      <c r="AA20" t="n">
         <v>242.6</v>
       </c>
-      <c r="AB20" s="2">
+      <c r="AB20" t="n">
         <v>267.7</v>
       </c>
-      <c r="AC20" s="2">
+      <c r="AC20" t="n">
         <v>338.7</v>
       </c>
-      <c r="AD20" s="2">
+      <c r="AD20" t="n">
         <v>292.3</v>
       </c>
-      <c r="AE20" s="2">
+      <c r="AE20" t="n">
         <v>256.3</v>
       </c>
-      <c r="AF20" s="2">
+      <c r="AF20" t="n">
         <v>109.7</v>
       </c>
-      <c r="AG20" s="2">
+      <c r="AG20" t="n">
         <v>230.3</v>
       </c>
-      <c r="AH20" s="2">
+      <c r="AH20" t="n">
         <v>310.8</v>
       </c>
-      <c r="AI20" s="2">
+      <c r="AI20" t="n">
         <v>256.3</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" t="n">
         <v>251.5</v>
       </c>
-      <c r="C21" s="2">
-        <v>321.10000000000002</v>
-      </c>
-      <c r="D21" s="2">
-        <v>264.60000000000002</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="C21" t="n">
+        <v>321.1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>264.6</v>
+      </c>
+      <c r="E21" t="n">
         <v>261.7</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" t="n">
         <v>229.6</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" t="n">
         <v>296.5</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" t="n">
         <v>153.9</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" t="n">
         <v>352.5</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" t="n">
         <v>260.8</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" t="n">
         <v>26.1</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" t="n">
         <v>168.9</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" t="n">
         <v>252.1</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21" t="n">
         <v>215.2</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" t="n">
         <v>271.3</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" t="n">
         <v>296.5</v>
       </c>
-      <c r="Q21" s="2">
-        <v>262.10000000000002</v>
-      </c>
-      <c r="R21" s="2">
+      <c r="Q21" t="n">
+        <v>262.1</v>
+      </c>
+      <c r="R21" t="n">
         <v>153.9</v>
       </c>
-      <c r="S21" s="2">
+      <c r="S21" t="n">
         <v>365.3</v>
       </c>
-      <c r="T21" s="2">
+      <c r="T21" t="n">
         <v>211.7</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="2">
+      <c r="V21" t="n">
         <v>283</v>
       </c>
-      <c r="W21" s="2">
+      <c r="W21" t="n">
         <v>287.2</v>
       </c>
-      <c r="X21" s="2">
+      <c r="X21" t="n">
         <v>254.4</v>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y21" t="n">
         <v>265.5</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="Z21" t="n">
         <v>249.1</v>
       </c>
-      <c r="AA21" s="2">
+      <c r="AA21" t="n">
         <v>275.2</v>
       </c>
-      <c r="AB21" s="2">
+      <c r="AB21" t="n">
         <v>300.3</v>
       </c>
-      <c r="AC21" s="2">
+      <c r="AC21" t="n">
         <v>371.3</v>
       </c>
-      <c r="AD21" s="2">
-        <v>324.89999999999998</v>
-      </c>
-      <c r="AE21" s="2">
-        <v>288.89999999999998</v>
-      </c>
-      <c r="AF21" s="2">
+      <c r="AD21" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="AF21" t="n">
         <v>178.6</v>
       </c>
-      <c r="AG21" s="2">
-        <v>262.89999999999998</v>
-      </c>
-      <c r="AH21" s="2">
+      <c r="AG21" t="n">
+        <v>262.9</v>
+      </c>
+      <c r="AH21" t="n">
         <v>343.4</v>
       </c>
-      <c r="AI21" s="2">
-        <v>288.89999999999998</v>
+      <c r="AI21" t="n">
+        <v>288.9</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" t="n">
         <v>31.1</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" t="n">
         <v>184.4</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" t="n">
         <v>29.8</v>
       </c>
-      <c r="E22" s="2">
-        <v>142.80000000000001</v>
-      </c>
-      <c r="F22" s="2">
-        <v>82.4</v>
-      </c>
-      <c r="G22" s="2">
-        <v>148.69999999999999</v>
-      </c>
-      <c r="H22" s="2">
+      <c r="E22" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="H22" t="n">
         <v>163</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" t="n">
         <v>233.6</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" t="n">
         <v>68.7</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" t="n">
         <v>211.8</v>
       </c>
-      <c r="L22" s="2">
+      <c r="L22" t="n">
         <v>247.7</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22" t="n">
         <v>148.4</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22" t="n">
         <v>118.2</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22" t="n">
         <v>78.8</v>
       </c>
-      <c r="P22" s="2">
-        <v>148.69999999999999</v>
-      </c>
-      <c r="Q22" s="2">
+      <c r="P22" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="Q22" t="n">
         <v>82</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R22" t="n">
         <v>163</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S22" t="n">
         <v>228.6</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T22" t="n">
         <v>134.5</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" t="n">
         <v>214.2</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V22" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="2">
+      <c r="W22" t="n">
         <v>107.1</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X22" t="n">
         <v>71.8</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y22" t="n">
         <v>55.4</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="Z22" t="n">
         <v>87.8</v>
       </c>
-      <c r="AA22" s="2">
+      <c r="AA22" t="n">
         <v>138.5</v>
       </c>
-      <c r="AB22" s="2">
+      <c r="AB22" t="n">
         <v>120.2</v>
       </c>
-      <c r="AC22" s="2">
+      <c r="AC22" t="n">
         <v>234.6</v>
       </c>
-      <c r="AD22" s="2">
+      <c r="AD22" t="n">
         <v>63.6</v>
       </c>
-      <c r="AE22" s="2">
+      <c r="AE22" t="n">
         <v>72.2</v>
       </c>
-      <c r="AF22" s="2">
+      <c r="AF22" t="n">
         <v>188.5</v>
       </c>
-      <c r="AG22" s="2">
+      <c r="AG22" t="n">
         <v>165.9</v>
       </c>
-      <c r="AH22" s="2">
+      <c r="AH22" t="n">
         <v>206.7</v>
       </c>
-      <c r="AI22" s="2">
+      <c r="AI22" t="n">
         <v>72.2</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" t="n">
         <v>100.5</v>
       </c>
-      <c r="C23" s="2">
-        <v>258.10000000000002</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="C23" t="n">
+        <v>258.1</v>
+      </c>
+      <c r="D23" t="n">
         <v>111.1</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" t="n">
         <v>208.2</v>
       </c>
-      <c r="F23" s="2">
-        <v>151.80000000000001</v>
-      </c>
-      <c r="G23" s="2">
+      <c r="F23" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="G23" t="n">
         <v>41.6</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" t="n">
         <v>171.5</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" t="n">
         <v>299</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" t="n">
         <v>60.1</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" t="n">
         <v>220.3</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" t="n">
         <v>256.2</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" t="n">
         <v>198.6</v>
       </c>
-      <c r="N23" s="2">
-        <v>161.69999999999999</v>
-      </c>
-      <c r="O23" s="2">
+      <c r="N23" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="O23" t="n">
         <v>70.2</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" t="n">
         <v>41.6</v>
       </c>
-      <c r="Q23" s="2">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="R23" s="2">
+      <c r="Q23" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="R23" t="n">
         <v>171.5</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S23" t="n">
         <v>302.3</v>
       </c>
-      <c r="T23" s="2">
+      <c r="T23" t="n">
         <v>143</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" t="n">
         <v>222.7</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V23" t="n">
         <v>105.5</v>
       </c>
-      <c r="W23" s="2">
+      <c r="W23" t="n">
         <v>0</v>
       </c>
-      <c r="X23" s="2">
+      <c r="X23" t="n">
         <v>64.3</v>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y23" t="n">
         <v>49.3</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="Z23" t="n">
         <v>161.5</v>
       </c>
-      <c r="AA23" s="2">
+      <c r="AA23" t="n">
         <v>212.2</v>
       </c>
-      <c r="AB23" s="2">
+      <c r="AB23" t="n">
         <v>13.1</v>
       </c>
-      <c r="AC23" s="2">
+      <c r="AC23" t="n">
         <v>308.3</v>
       </c>
-      <c r="AD23" s="2">
+      <c r="AD23" t="n">
         <v>110</v>
       </c>
-      <c r="AE23" s="2">
+      <c r="AE23" t="n">
         <v>145.9</v>
       </c>
-      <c r="AF23" s="2">
+      <c r="AF23" t="n">
         <v>197</v>
       </c>
-      <c r="AG23" s="2">
+      <c r="AG23" t="n">
         <v>209.4</v>
       </c>
-      <c r="AH23" s="2">
-        <v>280.39999999999998</v>
-      </c>
-      <c r="AI23" s="2">
+      <c r="AH23" t="n">
+        <v>280.4</v>
+      </c>
+      <c r="AI23" t="n">
         <v>145.9</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="2">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="C24" t="n">
         <v>229.2</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" t="n">
         <v>46.8</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" t="n">
         <v>169.8</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" t="n">
         <v>87.5</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" t="n">
         <v>109.3</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" t="n">
         <v>136.1</v>
       </c>
-      <c r="I24" s="2">
-        <v>260.60000000000002</v>
-      </c>
-      <c r="J24" s="2">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="K24" s="2">
+      <c r="I24" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="K24" t="n">
         <v>184.9</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" t="n">
         <v>220.8</v>
       </c>
-      <c r="M24" s="2">
-        <v>160.19999999999999</v>
-      </c>
-      <c r="N24" s="2">
+      <c r="M24" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="N24" t="n">
         <v>123.3</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24" t="n">
         <v>23.1</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" t="n">
         <v>109.3</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" t="n">
         <v>42.6</v>
       </c>
-      <c r="R24" s="2">
+      <c r="R24" t="n">
         <v>136.1</v>
       </c>
-      <c r="S24" s="2">
-        <v>273.39999999999998</v>
-      </c>
-      <c r="T24" s="2">
+      <c r="S24" t="n">
+        <v>273.4</v>
+      </c>
+      <c r="T24" t="n">
         <v>107.6</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" t="n">
         <v>187.3</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V24" t="n">
         <v>65.2</v>
       </c>
-      <c r="W24" s="2">
+      <c r="W24" t="n">
         <v>67.7</v>
       </c>
-      <c r="X24" s="2">
+      <c r="X24" t="n">
         <v>0</v>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y24" t="n">
         <v>46</v>
       </c>
-      <c r="Z24" s="2">
+      <c r="Z24" t="n">
         <v>140.1</v>
       </c>
-      <c r="AA24" s="2">
+      <c r="AA24" t="n">
         <v>183.3</v>
       </c>
-      <c r="AB24" s="2">
+      <c r="AB24" t="n">
         <v>80.8</v>
       </c>
-      <c r="AC24" s="2">
-        <v>279.39999999999998</v>
-      </c>
-      <c r="AD24" s="2">
+      <c r="AC24" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="AD24" t="n">
         <v>106.7</v>
       </c>
-      <c r="AE24" s="2">
+      <c r="AE24" t="n">
         <v>124.5</v>
       </c>
-      <c r="AF24" s="2">
+      <c r="AF24" t="n">
         <v>161.6</v>
       </c>
-      <c r="AG24" s="2">
+      <c r="AG24" t="n">
         <v>171</v>
       </c>
-      <c r="AH24" s="2">
+      <c r="AH24" t="n">
         <v>251.5</v>
       </c>
-      <c r="AI24" s="2">
+      <c r="AI24" t="n">
         <v>124.5</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" t="n">
         <v>63.3</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" t="n">
         <v>208.8</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" t="n">
         <v>62</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" t="n">
         <v>167.2</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" t="n">
         <v>114.6</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" t="n">
         <v>93.3</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" t="n">
         <v>146.6</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" t="n">
         <v>258</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" t="n">
         <v>13.3</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25" t="n">
         <v>195.4</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" t="n">
         <v>231.3</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25" t="n">
         <v>172.8</v>
       </c>
-      <c r="N25" s="2">
-        <v>136.80000000000001</v>
-      </c>
-      <c r="O25" s="2">
+      <c r="N25" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="O25" t="n">
         <v>23.4</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" t="n">
         <v>93.3</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" t="n">
         <v>26.6</v>
       </c>
-      <c r="R25" s="2">
+      <c r="R25" t="n">
         <v>146.6</v>
       </c>
-      <c r="S25" s="2">
+      <c r="S25" t="n">
         <v>253</v>
       </c>
-      <c r="T25" s="2">
+      <c r="T25" t="n">
         <v>118.1</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" t="n">
         <v>197.8</v>
       </c>
-      <c r="V25" s="2">
+      <c r="V25" t="n">
         <v>56.2</v>
       </c>
-      <c r="W25" s="2">
+      <c r="W25" t="n">
         <v>51.7</v>
       </c>
-      <c r="X25" s="2">
+      <c r="X25" t="n">
         <v>39.4</v>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y25" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="2">
+      <c r="Z25" t="n">
         <v>112.2</v>
       </c>
-      <c r="AA25" s="2">
+      <c r="AA25" t="n">
         <v>162.9</v>
       </c>
-      <c r="AB25" s="2">
+      <c r="AB25" t="n">
         <v>64.8</v>
       </c>
-      <c r="AC25" s="2">
+      <c r="AC25" t="n">
         <v>259</v>
       </c>
-      <c r="AD25" s="2">
+      <c r="AD25" t="n">
         <v>60.7</v>
       </c>
-      <c r="AE25" s="2">
-        <v>96.6</v>
-      </c>
-      <c r="AF25" s="2">
+      <c r="AE25" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AF25" t="n">
         <v>172.1</v>
       </c>
-      <c r="AG25" s="2">
+      <c r="AG25" t="n">
         <v>184.5</v>
       </c>
-      <c r="AH25" s="2">
+      <c r="AH25" t="n">
         <v>231.1</v>
       </c>
-      <c r="AI25" s="2">
-        <v>96.6</v>
+      <c r="AI25" t="n">
+        <v>96.59999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" t="n">
         <v>70</v>
       </c>
-      <c r="C26" s="2">
-        <v>96.6</v>
-      </c>
-      <c r="D26" s="2">
-        <v>83.1</v>
-      </c>
-      <c r="E26" s="2">
+      <c r="C26" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="E26" t="n">
         <v>55</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" t="n">
         <v>48.1</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" t="n">
         <v>191.8</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" t="n">
         <v>166.6</v>
       </c>
-      <c r="I26" s="2">
-        <v>145.80000000000001</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="I26" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="J26" t="n">
         <v>123.8</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26" t="n">
         <v>215.4</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26" t="n">
         <v>251.3</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" t="n">
         <v>60.6</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" t="n">
         <v>51.3</v>
       </c>
-      <c r="O26" s="2">
-        <v>128.19999999999999</v>
-      </c>
-      <c r="P26" s="2">
+      <c r="O26" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="P26" t="n">
         <v>191.8</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" t="n">
         <v>125.1</v>
       </c>
-      <c r="R26" s="2">
+      <c r="R26" t="n">
         <v>166.6</v>
       </c>
-      <c r="S26" s="2">
-        <v>140.80000000000001</v>
-      </c>
-      <c r="T26" s="2">
+      <c r="S26" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="T26" t="n">
         <v>138.1</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" t="n">
         <v>217.8</v>
       </c>
-      <c r="V26" s="2">
-        <v>85.4</v>
-      </c>
-      <c r="W26" s="2">
-        <v>150.19999999999999</v>
-      </c>
-      <c r="X26" s="2">
+      <c r="V26" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="W26" t="n">
+        <v>150.2</v>
+      </c>
+      <c r="X26" t="n">
         <v>105.1</v>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y26" t="n">
         <v>114.3</v>
       </c>
-      <c r="Z26" s="2">
+      <c r="Z26" t="n">
         <v>0</v>
       </c>
-      <c r="AA26" s="2">
+      <c r="AA26" t="n">
         <v>50.7</v>
       </c>
-      <c r="AB26" s="2">
-        <v>163.30000000000001</v>
-      </c>
-      <c r="AC26" s="2">
-        <v>146.80000000000001</v>
-      </c>
-      <c r="AD26" s="2">
+      <c r="AB26" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="AD26" t="n">
         <v>96.3</v>
       </c>
-      <c r="AE26" s="2">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="AF26" s="2">
+      <c r="AE26" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="AF26" t="n">
         <v>192.1</v>
       </c>
-      <c r="AG26" s="2">
+      <c r="AG26" t="n">
         <v>169.5</v>
       </c>
-      <c r="AH26" s="2">
+      <c r="AH26" t="n">
         <v>118.9</v>
       </c>
-      <c r="AI26" s="2">
-        <v>39.799999999999997</v>
+      <c r="AI26" t="n">
+        <v>39.8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="27">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" t="n">
         <v>91.3</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" t="n">
         <v>45.9</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" t="n">
         <v>104.4</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" t="n">
         <v>76.3</v>
       </c>
-      <c r="F27" s="2">
-        <v>69.400000000000006</v>
-      </c>
-      <c r="G27" s="2">
+      <c r="F27" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="G27" t="n">
         <v>213.1</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" t="n">
         <v>187.9</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" t="n">
         <v>167.1</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" t="n">
         <v>145.1</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" t="n">
         <v>236.7</v>
       </c>
-      <c r="L27" s="2">
-        <v>272.60000000000002</v>
-      </c>
-      <c r="M27" s="2">
-        <v>81.900000000000006</v>
-      </c>
-      <c r="N27" s="2">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="O27" s="2">
+      <c r="L27" t="n">
+        <v>272.6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="N27" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="O27" t="n">
         <v>149.5</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" t="n">
         <v>213.1</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" t="n">
         <v>146.4</v>
       </c>
-      <c r="R27" s="2">
+      <c r="R27" t="n">
         <v>187.9</v>
       </c>
-      <c r="S27" s="2">
-        <v>90.1</v>
-      </c>
-      <c r="T27" s="2">
+      <c r="S27" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="T27" t="n">
         <v>159.4</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" t="n">
         <v>239.1</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V27" t="n">
         <v>122.8</v>
       </c>
-      <c r="W27" s="2">
+      <c r="W27" t="n">
         <v>171.5</v>
       </c>
-      <c r="X27" s="2">
+      <c r="X27" t="n">
         <v>126.4</v>
       </c>
-      <c r="Y27" s="2">
-        <v>146.69999999999999</v>
-      </c>
-      <c r="Z27" s="2">
+      <c r="Y27" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="Z27" t="n">
         <v>54.1</v>
       </c>
-      <c r="AA27" s="2">
+      <c r="AA27" t="n">
         <v>0</v>
       </c>
-      <c r="AB27" s="2">
+      <c r="AB27" t="n">
         <v>184.6</v>
       </c>
-      <c r="AC27" s="2">
-        <v>96.1</v>
-      </c>
-      <c r="AD27" s="2">
+      <c r="AC27" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="AD27" t="n">
         <v>150.4</v>
       </c>
-      <c r="AE27" s="2">
-        <v>93.9</v>
-      </c>
-      <c r="AF27" s="2">
+      <c r="AE27" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="AF27" t="n">
         <v>213.4</v>
       </c>
-      <c r="AG27" s="2">
+      <c r="AG27" t="n">
         <v>190.8</v>
       </c>
-      <c r="AH27" s="2">
+      <c r="AH27" t="n">
         <v>104</v>
       </c>
-      <c r="AI27" s="2">
-        <v>93.9</v>
+      <c r="AI27" t="n">
+        <v>93.90000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="28">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" t="n">
         <v>110</v>
       </c>
-      <c r="C28" s="2">
-        <v>267.60000000000002</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="C28" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="D28" t="n">
         <v>120.6</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" t="n">
         <v>217.7</v>
       </c>
-      <c r="F28" s="2">
-        <v>161.30000000000001</v>
-      </c>
-      <c r="G28" s="2">
+      <c r="F28" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="G28" t="n">
         <v>47.9</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" t="n">
         <v>181</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" t="n">
         <v>308.5</v>
       </c>
-      <c r="J28" s="2">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="K28" s="2">
+      <c r="J28" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="K28" t="n">
         <v>229.8</v>
       </c>
-      <c r="L28" s="2">
+      <c r="L28" t="n">
         <v>265.7</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28" t="n">
         <v>208.1</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" t="n">
         <v>171.2</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28" t="n">
         <v>79.7</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" t="n">
         <v>47.9</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" t="n">
         <v>48.8</v>
       </c>
-      <c r="R28" s="2">
+      <c r="R28" t="n">
         <v>181</v>
       </c>
-      <c r="S28" s="2">
+      <c r="S28" t="n">
         <v>311.8</v>
       </c>
-      <c r="T28" s="2">
+      <c r="T28" t="n">
         <v>152.5</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" t="n">
         <v>232.2</v>
       </c>
-      <c r="V28" s="2">
+      <c r="V28" t="n">
         <v>115</v>
       </c>
-      <c r="W28" s="2">
+      <c r="W28" t="n">
         <v>9.5</v>
       </c>
-      <c r="X28" s="2">
+      <c r="X28" t="n">
         <v>73.8</v>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y28" t="n">
         <v>58.8</v>
       </c>
-      <c r="Z28" s="2">
+      <c r="Z28" t="n">
         <v>171</v>
       </c>
-      <c r="AA28" s="2">
+      <c r="AA28" t="n">
         <v>221.7</v>
       </c>
-      <c r="AB28" s="2">
+      <c r="AB28" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" s="2">
+      <c r="AC28" t="n">
         <v>317.8</v>
       </c>
-      <c r="AD28" s="2">
+      <c r="AD28" t="n">
         <v>119.5</v>
       </c>
-      <c r="AE28" s="2">
+      <c r="AE28" t="n">
         <v>155.4</v>
       </c>
-      <c r="AF28" s="2">
+      <c r="AF28" t="n">
         <v>206.5</v>
       </c>
-      <c r="AG28" s="2">
+      <c r="AG28" t="n">
         <v>218.9</v>
       </c>
-      <c r="AH28" s="2">
-        <v>289.89999999999998</v>
-      </c>
-      <c r="AI28" s="2">
+      <c r="AH28" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="AI28" t="n">
         <v>155.4</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="29">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" t="n">
         <v>187.8</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" t="n">
         <v>117.5</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" t="n">
         <v>200.9</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" t="n">
         <v>172.8</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" t="n">
         <v>165.9</v>
       </c>
-      <c r="G29" s="2">
-        <v>309.60000000000002</v>
-      </c>
-      <c r="H29" s="2">
-        <v>284.39999999999998</v>
-      </c>
-      <c r="I29" s="2">
+      <c r="G29" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="I29" t="n">
         <v>257.5</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" t="n">
         <v>241.6</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" t="n">
         <v>333.2</v>
       </c>
-      <c r="L29" s="2">
+      <c r="L29" t="n">
         <v>369.1</v>
       </c>
-      <c r="M29" s="2">
+      <c r="M29" t="n">
         <v>178.4</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N29" t="n">
         <v>169.1</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O29" t="n">
         <v>246</v>
       </c>
-      <c r="P29" s="2">
-        <v>309.60000000000002</v>
-      </c>
-      <c r="Q29" s="2">
+      <c r="P29" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="Q29" t="n">
         <v>242.9</v>
       </c>
-      <c r="R29" s="2">
-        <v>284.39999999999998</v>
-      </c>
-      <c r="S29" s="2">
+      <c r="R29" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="S29" t="n">
         <v>45</v>
       </c>
-      <c r="T29" s="2">
+      <c r="T29" t="n">
         <v>255.9</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" t="n">
         <v>335.6</v>
       </c>
-      <c r="V29" s="2">
+      <c r="V29" t="n">
         <v>219.3</v>
       </c>
-      <c r="W29" s="2">
+      <c r="W29" t="n">
         <v>268</v>
       </c>
-      <c r="X29" s="2">
+      <c r="X29" t="n">
         <v>222.9</v>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y29" t="n">
         <v>243.2</v>
       </c>
-      <c r="Z29" s="2">
+      <c r="Z29" t="n">
         <v>150.6</v>
       </c>
-      <c r="AA29" s="2">
+      <c r="AA29" t="n">
         <v>96.5</v>
       </c>
-      <c r="AB29" s="2">
-        <v>281.10000000000002</v>
-      </c>
-      <c r="AC29" s="2">
+      <c r="AB29" t="n">
+        <v>281.1</v>
+      </c>
+      <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="2">
+      <c r="AD29" t="n">
         <v>246.9</v>
       </c>
-      <c r="AE29" s="2">
+      <c r="AE29" t="n">
         <v>190.4</v>
       </c>
-      <c r="AF29" s="2">
-        <v>309.89999999999998</v>
-      </c>
-      <c r="AG29" s="2">
+      <c r="AF29" t="n">
+        <v>309.9</v>
+      </c>
+      <c r="AG29" t="n">
         <v>287.3</v>
       </c>
-      <c r="AH29" s="2">
+      <c r="AH29" t="n">
         <v>87.7</v>
       </c>
-      <c r="AI29" s="2">
+      <c r="AI29" t="n">
         <v>190.4</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="30">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="2">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="C30" t="n">
         <v>189.4</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" t="n">
         <v>68.3</v>
       </c>
-      <c r="E30" s="2">
-        <v>147.80000000000001</v>
-      </c>
-      <c r="F30" s="2">
+      <c r="E30" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="F30" t="n">
         <v>120.9</v>
       </c>
-      <c r="G30" s="2">
-        <v>149.69999999999999</v>
-      </c>
-      <c r="H30" s="2">
+      <c r="G30" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="H30" t="n">
         <v>201.5</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" t="n">
         <v>238.6</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" t="n">
         <v>69.7</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30" t="n">
         <v>250.3</v>
       </c>
-      <c r="L30" s="2">
+      <c r="L30" t="n">
         <v>286.2</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30" t="n">
         <v>153.4</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" t="n">
         <v>144.1</v>
       </c>
-      <c r="O30" s="2">
+      <c r="O30" t="n">
         <v>79.8</v>
       </c>
-      <c r="P30" s="2">
-        <v>149.69999999999999</v>
-      </c>
-      <c r="Q30" s="2">
+      <c r="P30" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="Q30" t="n">
         <v>83</v>
       </c>
-      <c r="R30" s="2">
+      <c r="R30" t="n">
         <v>201.5</v>
       </c>
-      <c r="S30" s="2">
+      <c r="S30" t="n">
         <v>233.6</v>
       </c>
-      <c r="T30" s="2">
+      <c r="T30" t="n">
         <v>173</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" t="n">
         <v>252.7</v>
       </c>
-      <c r="V30" s="2">
+      <c r="V30" t="n">
         <v>62.5</v>
       </c>
-      <c r="W30" s="2">
+      <c r="W30" t="n">
         <v>108.1</v>
       </c>
-      <c r="X30" s="2">
+      <c r="X30" t="n">
         <v>95.8</v>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y30" t="n">
         <v>56.4</v>
       </c>
-      <c r="Z30" s="2">
+      <c r="Z30" t="n">
         <v>92.8</v>
       </c>
-      <c r="AA30" s="2">
+      <c r="AA30" t="n">
         <v>143.5</v>
       </c>
-      <c r="AB30" s="2">
+      <c r="AB30" t="n">
         <v>121.2</v>
       </c>
-      <c r="AC30" s="2">
+      <c r="AC30" t="n">
         <v>239.6</v>
       </c>
-      <c r="AD30" s="2">
+      <c r="AD30" t="n">
         <v>0</v>
       </c>
-      <c r="AE30" s="2">
+      <c r="AE30" t="n">
         <v>77.2</v>
       </c>
-      <c r="AF30" s="2">
+      <c r="AF30" t="n">
         <v>227</v>
       </c>
-      <c r="AG30" s="2">
+      <c r="AG30" t="n">
         <v>204.4</v>
       </c>
-      <c r="AH30" s="2">
+      <c r="AH30" t="n">
         <v>211.7</v>
       </c>
-      <c r="AI30" s="2">
+      <c r="AI30" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="31">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="2">
-        <v>86.1</v>
-      </c>
-      <c r="C31" s="2">
+      <c r="B31" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="C31" t="n">
         <v>130.9</v>
       </c>
-      <c r="D31" s="2">
-        <v>90.9</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="D31" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E31" t="n">
         <v>89.3</v>
       </c>
-      <c r="F31" s="2">
-        <v>82.4</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="F31" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="G31" t="n">
         <v>196.8</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" t="n">
         <v>200.9</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" t="n">
         <v>180.1</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" t="n">
         <v>116.8</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" t="n">
         <v>249.7</v>
       </c>
-      <c r="L31" s="2">
-        <v>285.60000000000002</v>
-      </c>
-      <c r="M31" s="2">
-        <v>94.9</v>
-      </c>
-      <c r="N31" s="2">
-        <v>85.6</v>
-      </c>
-      <c r="O31" s="2">
+      <c r="L31" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="N31" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="O31" t="n">
         <v>126.9</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" t="n">
         <v>196.8</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" t="n">
         <v>130.1</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" t="n">
         <v>200.9</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31" t="n">
         <v>175.1</v>
       </c>
-      <c r="T31" s="2">
+      <c r="T31" t="n">
         <v>172.4</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" t="n">
         <v>252.1</v>
       </c>
-      <c r="V31" s="2">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="W31" s="2">
-        <v>155.19999999999999</v>
-      </c>
-      <c r="X31" s="2">
+      <c r="V31" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="W31" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="X31" t="n">
         <v>126.8</v>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y31" t="n">
         <v>103.5</v>
       </c>
-      <c r="Z31" s="2">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="AA31" s="2">
+      <c r="Z31" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="AA31" t="n">
         <v>85</v>
       </c>
-      <c r="AB31" s="2">
+      <c r="AB31" t="n">
         <v>168.3</v>
       </c>
-      <c r="AC31" s="2">
+      <c r="AC31" t="n">
         <v>181.1</v>
       </c>
-      <c r="AD31" s="2">
+      <c r="AD31" t="n">
         <v>85.5</v>
       </c>
-      <c r="AE31" s="2">
+      <c r="AE31" t="n">
         <v>0</v>
       </c>
-      <c r="AF31" s="2">
+      <c r="AF31" t="n">
         <v>226.4</v>
       </c>
-      <c r="AG31" s="2">
+      <c r="AG31" t="n">
         <v>203.8</v>
       </c>
-      <c r="AH31" s="2">
-        <v>153.19999999999999</v>
-      </c>
-      <c r="AI31" s="2">
+      <c r="AH31" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="AI31" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="32">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" t="n">
         <v>242.6</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" t="n">
         <v>312.2</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" t="n">
         <v>255.7</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" t="n">
         <v>252.8</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" t="n">
         <v>220.7</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" t="n">
         <v>240</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" t="n">
         <v>74.3</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" t="n">
         <v>343.6</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" t="n">
         <v>251.9</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" t="n">
         <v>123.1</v>
       </c>
-      <c r="L32" s="2">
+      <c r="L32" t="n">
         <v>59.2</v>
       </c>
-      <c r="M32" s="2">
+      <c r="M32" t="n">
         <v>243.2</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N32" t="n">
         <v>206.3</v>
       </c>
-      <c r="O32" s="2">
-        <v>262.39999999999998</v>
-      </c>
-      <c r="P32" s="2">
+      <c r="O32" t="n">
+        <v>262.4</v>
+      </c>
+      <c r="P32" t="n">
         <v>240</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" t="n">
         <v>253.2</v>
       </c>
-      <c r="R32" s="2">
+      <c r="R32" t="n">
         <v>74.3</v>
       </c>
-      <c r="S32" s="2">
+      <c r="S32" t="n">
         <v>356.4</v>
       </c>
-      <c r="T32" s="2">
+      <c r="T32" t="n">
         <v>202.8</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" t="n">
         <v>125.5</v>
       </c>
-      <c r="V32" s="2">
-        <v>274.10000000000002</v>
-      </c>
-      <c r="W32" s="2">
+      <c r="V32" t="n">
+        <v>274.1</v>
+      </c>
+      <c r="W32" t="n">
         <v>278.3</v>
       </c>
-      <c r="X32" s="2">
+      <c r="X32" t="n">
         <v>245.5</v>
       </c>
-      <c r="Y32" s="2">
-        <v>256.60000000000002</v>
-      </c>
-      <c r="Z32" s="2">
+      <c r="Y32" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="Z32" t="n">
         <v>240.2</v>
       </c>
-      <c r="AA32" s="2">
+      <c r="AA32" t="n">
         <v>266.3</v>
       </c>
-      <c r="AB32" s="2">
-        <v>283.39999999999998</v>
-      </c>
-      <c r="AC32" s="2">
+      <c r="AB32" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="AC32" t="n">
         <v>362.4</v>
       </c>
-      <c r="AD32" s="2">
+      <c r="AD32" t="n">
         <v>316</v>
       </c>
-      <c r="AE32" s="2">
+      <c r="AE32" t="n">
         <v>280</v>
       </c>
-      <c r="AF32" s="2">
+      <c r="AF32" t="n">
         <v>0</v>
       </c>
-      <c r="AG32" s="2">
+      <c r="AG32" t="n">
         <v>254</v>
       </c>
-      <c r="AH32" s="2">
+      <c r="AH32" t="n">
         <v>334.5</v>
       </c>
-      <c r="AI32" s="2">
+      <c r="AI32" t="n">
         <v>280</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="33">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" t="n">
         <v>183</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" t="n">
         <v>252.6</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" t="n">
         <v>196.1</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" t="n">
         <v>193.2</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" t="n">
         <v>161.1</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" t="n">
         <v>304.8</v>
       </c>
-      <c r="H33" s="2">
-        <v>279.60000000000002</v>
-      </c>
-      <c r="I33" s="2">
+      <c r="H33" t="n">
+        <v>279.6</v>
+      </c>
+      <c r="I33" t="n">
         <v>284</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" t="n">
         <v>236.8</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K33" t="n">
         <v>328.4</v>
       </c>
-      <c r="L33" s="2">
+      <c r="L33" t="n">
         <v>364.3</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33" t="n">
         <v>183.6</v>
       </c>
-      <c r="N33" s="2">
-        <v>146.69999999999999</v>
-      </c>
-      <c r="O33" s="2">
+      <c r="N33" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="O33" t="n">
         <v>241.2</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" t="n">
         <v>304.8</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" t="n">
         <v>238.1</v>
       </c>
-      <c r="R33" s="2">
-        <v>279.60000000000002</v>
-      </c>
-      <c r="S33" s="2">
+      <c r="R33" t="n">
+        <v>279.6</v>
+      </c>
+      <c r="S33" t="n">
         <v>296.8</v>
       </c>
-      <c r="T33" s="2">
+      <c r="T33" t="n">
         <v>251.1</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" t="n">
         <v>330.8</v>
       </c>
-      <c r="V33" s="2">
+      <c r="V33" t="n">
         <v>214.5</v>
       </c>
-      <c r="W33" s="2">
+      <c r="W33" t="n">
         <v>263.2</v>
       </c>
-      <c r="X33" s="2">
+      <c r="X33" t="n">
         <v>218.1</v>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y33" t="n">
         <v>238.4</v>
       </c>
-      <c r="Z33" s="2">
+      <c r="Z33" t="n">
         <v>180.6</v>
       </c>
-      <c r="AA33" s="2">
+      <c r="AA33" t="n">
         <v>206.7</v>
       </c>
-      <c r="AB33" s="2">
+      <c r="AB33" t="n">
         <v>276.3</v>
       </c>
-      <c r="AC33" s="2">
+      <c r="AC33" t="n">
         <v>302.8</v>
       </c>
-      <c r="AD33" s="2">
-        <v>256.39999999999998</v>
-      </c>
-      <c r="AE33" s="2">
+      <c r="AD33" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="AE33" t="n">
         <v>220.4</v>
       </c>
-      <c r="AF33" s="2">
-        <v>305.10000000000002</v>
-      </c>
-      <c r="AG33" s="2">
+      <c r="AF33" t="n">
+        <v>305.1</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0</v>
       </c>
-      <c r="AH33" s="2">
-        <v>274.89999999999998</v>
-      </c>
-      <c r="AI33" s="2">
+      <c r="AH33" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="AI33" t="n">
         <v>220.4</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="34">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" t="n">
         <v>146.6</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" t="n">
         <v>111.3</v>
       </c>
-      <c r="D34" s="2">
-        <v>159.69999999999999</v>
-      </c>
-      <c r="E34" s="2">
+      <c r="D34" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="E34" t="n">
         <v>131.6</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" t="n">
         <v>124.7</v>
       </c>
-      <c r="G34" s="2">
-        <v>268.39999999999998</v>
-      </c>
-      <c r="H34" s="2">
+      <c r="G34" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="H34" t="n">
         <v>243.2</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34" t="n">
         <v>169.8</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" t="n">
         <v>200.4</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" t="n">
         <v>292</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34" t="n">
         <v>327.9</v>
       </c>
-      <c r="M34" s="2">
-        <v>137.19999999999999</v>
-      </c>
-      <c r="N34" s="2">
+      <c r="M34" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="N34" t="n">
         <v>127.9</v>
       </c>
-      <c r="O34" s="2">
+      <c r="O34" t="n">
         <v>204.8</v>
       </c>
-      <c r="P34" s="2">
-        <v>268.39999999999998</v>
-      </c>
-      <c r="Q34" s="2">
+      <c r="P34" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="Q34" t="n">
         <v>201.7</v>
       </c>
-      <c r="R34" s="2">
+      <c r="R34" t="n">
         <v>243.2</v>
       </c>
-      <c r="S34" s="2">
+      <c r="S34" t="n">
         <v>78.3</v>
       </c>
-      <c r="T34" s="2">
+      <c r="T34" t="n">
         <v>214.7</v>
       </c>
-      <c r="U34" s="2">
-        <v>294.39999999999998</v>
-      </c>
-      <c r="V34" s="2">
+      <c r="U34" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="V34" t="n">
         <v>178.1</v>
       </c>
-      <c r="W34" s="2">
+      <c r="W34" t="n">
         <v>226.8</v>
       </c>
-      <c r="X34" s="2">
+      <c r="X34" t="n">
         <v>181.7</v>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y34" t="n">
         <v>202</v>
       </c>
-      <c r="Z34" s="2">
+      <c r="Z34" t="n">
         <v>109.4</v>
       </c>
-      <c r="AA34" s="2">
-        <v>88.4</v>
-      </c>
-      <c r="AB34" s="2">
+      <c r="AA34" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="AB34" t="n">
         <v>239.9</v>
       </c>
-      <c r="AC34" s="2">
-        <v>88.9</v>
-      </c>
-      <c r="AD34" s="2">
+      <c r="AC34" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="AD34" t="n">
         <v>205.7</v>
       </c>
-      <c r="AE34" s="2">
-        <v>149.19999999999999</v>
-      </c>
-      <c r="AF34" s="2">
+      <c r="AE34" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="AF34" t="n">
         <v>268.7</v>
       </c>
-      <c r="AG34" s="2">
+      <c r="AG34" t="n">
         <v>246.1</v>
       </c>
-      <c r="AH34" s="2">
+      <c r="AH34" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" s="2">
-        <v>149.19999999999999</v>
+      <c r="AI34" t="n">
+        <v>149.2</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="35">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="2">
-        <v>86.1</v>
-      </c>
-      <c r="C35" s="2">
+      <c r="B35" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="C35" t="n">
         <v>130.9</v>
       </c>
-      <c r="D35" s="2">
-        <v>90.9</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="D35" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E35" t="n">
         <v>89.3</v>
       </c>
-      <c r="F35" s="2">
-        <v>82.4</v>
-      </c>
-      <c r="G35" s="2">
+      <c r="F35" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="G35" t="n">
         <v>196.8</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" t="n">
         <v>200.9</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" t="n">
         <v>180.1</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" t="n">
         <v>116.8</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K35" t="n">
         <v>249.7</v>
       </c>
-      <c r="L35" s="2">
-        <v>285.60000000000002</v>
-      </c>
-      <c r="M35" s="2">
-        <v>94.9</v>
-      </c>
-      <c r="N35" s="2">
-        <v>85.6</v>
-      </c>
-      <c r="O35" s="2">
+      <c r="L35" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="N35" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="O35" t="n">
         <v>126.9</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" t="n">
         <v>196.8</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" t="n">
         <v>130.1</v>
       </c>
-      <c r="R35" s="2">
+      <c r="R35" t="n">
         <v>200.9</v>
       </c>
-      <c r="S35" s="2">
+      <c r="S35" t="n">
         <v>175.1</v>
       </c>
-      <c r="T35" s="2">
+      <c r="T35" t="n">
         <v>172.4</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" t="n">
         <v>252.1</v>
       </c>
-      <c r="V35" s="2">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="W35" s="2">
-        <v>155.19999999999999</v>
-      </c>
-      <c r="X35" s="2">
+      <c r="V35" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="W35" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="X35" t="n">
         <v>126.8</v>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y35" t="n">
         <v>103.5</v>
       </c>
-      <c r="Z35" s="2">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="AA35" s="2">
+      <c r="Z35" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="AA35" t="n">
         <v>85</v>
       </c>
-      <c r="AB35" s="2">
+      <c r="AB35" t="n">
         <v>168.3</v>
       </c>
-      <c r="AC35" s="2">
+      <c r="AC35" t="n">
         <v>181.1</v>
       </c>
-      <c r="AD35" s="2">
+      <c r="AD35" t="n">
         <v>85.5</v>
       </c>
-      <c r="AE35" s="2">
+      <c r="AE35" t="n">
         <v>0</v>
       </c>
-      <c r="AF35" s="2">
+      <c r="AF35" t="n">
         <v>226.4</v>
       </c>
-      <c r="AG35" s="2">
+      <c r="AG35" t="n">
         <v>203.8</v>
       </c>
-      <c r="AH35" s="2">
-        <v>153.19999999999999</v>
-      </c>
-      <c r="AI35" s="2">
+      <c r="AH35" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="AI35" t="n">
         <v>0</v>
       </c>
     </row>
